--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DDE556-CE07-4423-A9B2-885286DE5EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE64AC9A-C183-44B3-B466-3DD4B632F7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,13 +107,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ReturnToTitlePanel内</t>
-    <rPh sb="18" eb="19">
-      <t>ナイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タイトルへ戻りますか？</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -363,6 +356,9 @@
     <t>Tem certeza de que deseja excluir os dados salvos?
 (Uma vez excluídos, os dados não poderão ser recuperados.)</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReturnToTitlePanel内とGameOver画面内</t>
   </si>
 </sst>
 </file>
@@ -735,7 +731,7 @@
     <col min="11" max="11" width="21.625" customWidth="1"/>
     <col min="12" max="12" width="27.75" customWidth="1"/>
     <col min="13" max="13" width="25.625" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
+    <col min="14" max="14" width="38.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -755,28 +751,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
       <c r="H1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
-        <v>44</v>
-      </c>
       <c r="L1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" t="s">
         <v>52</v>
-      </c>
-      <c r="M1" t="s">
-        <v>53</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>15</v>
@@ -799,25 +795,25 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" s="5">
         <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K2">
         <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M2">
         <v>8</v>
@@ -828,37 +824,37 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3">
         <v>12</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" s="5">
         <v>12</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K3">
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -881,25 +877,25 @@
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3">
         <v>16</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" s="5">
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4">
         <v>12</v>
@@ -922,25 +918,25 @@
         <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="3">
         <v>32</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I5" s="5">
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5">
         <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M5">
         <v>32</v>
@@ -963,25 +959,25 @@
         <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3">
         <v>32</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="5">
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6">
         <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M6">
         <v>32</v>
@@ -1004,72 +1000,72 @@
         <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3">
         <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7" s="5">
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M7">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="56.25">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3">
         <v>14</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8" s="5">
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K8">
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M8">
         <v>14</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="337.5">
@@ -1077,37 +1073,37 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" s="5">
         <v>20</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K9">
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M9">
         <v>16</v>
@@ -1118,37 +1114,37 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10">
         <v>14</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K10">
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M10">
         <v>8</v>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE64AC9A-C183-44B3-B466-3DD4B632F7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829C4B18-2C1F-4B6F-965A-62FD25B77204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -359,6 +359,30 @@
   </si>
   <si>
     <t>ReturnToTitlePanel内とGameOver画面内</t>
+  </si>
+  <si>
+    <t>ステージ選択へ戻りますか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Return to stage selection?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返回关卡选择？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返回關卡選擇？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>¿Volver a la selección de escenario?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Voltar à seleção de fases?</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -420,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -436,6 +460,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -727,7 +752,7 @@
     <col min="7" max="7" width="21.75" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
     <col min="9" max="9" width="22.75" customWidth="1"/>
-    <col min="10" max="10" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="34.625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.625" customWidth="1"/>
     <col min="12" max="12" width="27.75" customWidth="1"/>
     <col min="13" max="13" width="25.625" customWidth="1"/>
@@ -1150,11 +1175,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11">
+        <v>14</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829C4B18-2C1F-4B6F-965A-62FD25B77204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7ABB69-DE20-4454-985A-D2A77BEB0E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -383,6 +383,55 @@
   <si>
     <t>Voltar à seleção de fases?</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Пробел, Enter, ЛКМ…
+продолжить диалог</t>
+  </si>
+  <si>
+    <t>W, A, S, D или I, J, K, L… Движение
+Shift, +… Бег
+Мышь… Обзор
+ЛКМ… Взаимодействие
+ПКМ, E или U… Использовать предмет
+F или H… Фонарик
+P, Z или ESC… Пауза/Продолжить/Назад
+Ctrl, ?… Оглянуться</t>
+  </si>
+  <si>
+    <t>Время прохождения</t>
+  </si>
+  <si>
+    <t>Грёза</t>
+  </si>
+  <si>
+    <t>Морок</t>
+  </si>
+  <si>
+    <t>Кошмар</t>
+  </si>
+  <si>
+    <t>Вернуться в главное меню?</t>
+  </si>
+  <si>
+    <t>Спасибо, что сыграли в демоверсию!
+Свежие новости мы публикуем в
+X (@Tomanegi0707) и BlueSky (@tomanegi0707.bsky.social)!
+Будем очень благодарны, если вы пройдёте опрос,
+подпишетесь на нас и добавите игру в список желаемого!</t>
+  </si>
+  <si>
+    <t>Вы точно хотите удалить сохранённые данные?
+(Удалённые данные восстановить нельзя.)</t>
+  </si>
+  <si>
+    <t>Вернуться к выбору этапа?</t>
   </si>
 </sst>
 </file>
@@ -741,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -756,10 +805,12 @@
     <col min="11" max="11" width="21.625" customWidth="1"/>
     <col min="12" max="12" width="27.75" customWidth="1"/>
     <col min="13" max="13" width="25.625" customWidth="1"/>
-    <col min="14" max="14" width="38.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,11 +850,17 @@
       <c r="M1" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="75">
+    <row r="2" spans="1:16" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -843,8 +900,14 @@
       <c r="M2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="300">
+      <c r="N2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -884,8 +947,14 @@
       <c r="M3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="N3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>2</v>
       </c>
@@ -925,8 +994,14 @@
       <c r="M4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4" t="s">
+        <v>79</v>
+      </c>
+      <c r="O4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>3</v>
       </c>
@@ -966,8 +1041,14 @@
       <c r="M5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1007,8 +1088,14 @@
       <c r="M6">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1048,8 +1135,14 @@
       <c r="M7">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" t="s">
+        <v>82</v>
+      </c>
+      <c r="O7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1089,11 +1182,17 @@
       <c r="M8">
         <v>14</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8">
+        <v>14</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="337.5">
+    <row r="9" spans="1:16" ht="337.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1133,8 +1232,14 @@
       <c r="M9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="112.5">
+      <c r="N9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="112.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1174,8 +1279,14 @@
       <c r="M10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="37.5">
+      <c r="N10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1215,28 +1326,34 @@
       <c r="M11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" t="s">
+        <v>86</v>
+      </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7ABB69-DE20-4454-985A-D2A77BEB0E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBAA866-D1EF-4929-95AC-645E9DE8D3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1283,7 +1283,7 @@
         <v>85</v>
       </c>
       <c r="O10">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="37.5">

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBAA866-D1EF-4929-95AC-645E9DE8D3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3524939C-0129-4931-8704-ACC1588639AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -432,6 +432,55 @@
   </si>
   <si>
     <t>Вернуться к выбору этапа?</t>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Leertaste, Enter, Linksklick …
+Gespräch fortsetzen</t>
+  </si>
+  <si>
+    <t>W, A, S, D oder I, J, K, L … Bewegen
+Shift, + … Sprinten
+Maus … Umsehen
+Linksklick … Interagieren
+Rechtsklick oder E oder U … Gegenstand benutzen
+F oder H … Taschenlampe
+P oder Z oder ESC … Pause/Fortsetzen/Zurück
+Strg, ? … Umdrehen</t>
+  </si>
+  <si>
+    <t>Spielzeit</t>
+  </si>
+  <si>
+    <t>Träumerei</t>
+  </si>
+  <si>
+    <t>Trugbild</t>
+  </si>
+  <si>
+    <t>Albtraum</t>
+  </si>
+  <si>
+    <t>Zum Titelbildschirm zurückkehren?</t>
+  </si>
+  <si>
+    <t>Vielen Dank, dass du die Demo gespielt hast!
+Neuigkeiten gibt es laufend auf
+X (@Tomanegi0707) und BlueSky (@tomanegi0707.bsky.social)!
+Wir würden uns sehr freuen, wenn du an der Umfrage teilnimmst,
+uns folgst und das Spiel auf deine Wunschliste setzt!</t>
+  </si>
+  <si>
+    <t>Möchtest du deine Speicherdaten wirklich löschen?
+(Gelöschte Daten können nicht wiederhergestellt werden.)</t>
+  </si>
+  <si>
+    <t>Zur Stufenauswahl zurückkehren?</t>
   </si>
 </sst>
 </file>
@@ -790,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -807,10 +856,12 @@
     <col min="13" max="13" width="25.625" customWidth="1"/>
     <col min="14" max="14" width="47" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="38.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -856,11 +907,17 @@
       <c r="O1" t="s">
         <v>76</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="75">
+    <row r="2" spans="1:18" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -906,8 +963,14 @@
       <c r="O2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="300">
+      <c r="P2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -953,8 +1016,14 @@
       <c r="O3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="P3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1000,8 +1069,14 @@
       <c r="O4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="P4" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1047,8 +1122,14 @@
       <c r="O5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="P5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1094,8 +1175,14 @@
       <c r="O6">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="P6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1141,8 +1228,14 @@
       <c r="O7">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="P7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1188,11 +1281,17 @@
       <c r="O8">
         <v>14</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q8">
+        <v>13</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="337.5">
+    <row r="9" spans="1:18" ht="337.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1238,8 +1337,14 @@
       <c r="O9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="112.5">
+      <c r="P9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="112.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1285,8 +1390,14 @@
       <c r="O10">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="37.5">
+      <c r="P10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1332,28 +1443,34 @@
       <c r="O11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="P11" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3524939C-0129-4931-8704-ACC1588639AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970E6C46-8AB5-44D0-B8C7-AF6BDA1652C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -481,6 +481,55 @@
   </si>
   <si>
     <t>Zur Stufenauswahl zurückkehren?</t>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>Espace, Entrée, clic gauche…
+faire avancer le dialogue</t>
+  </si>
+  <si>
+    <t>W, A, S, D ou I, J, K, L… Se déplacer
+Shift, +… Courir
+Souris… Regarder
+Clic gauche… Interagir
+Clic droit, E ou U… Utiliser un objet
+F ou H… Lampe torche
+P, Z ou Échap… Pause/Reprendre/Retour
+Ctrl, ?… Se retourner</t>
+  </si>
+  <si>
+    <t>Temps de jeu</t>
+  </si>
+  <si>
+    <t>Rêverie</t>
+  </si>
+  <si>
+    <t>Chimère</t>
+  </si>
+  <si>
+    <t>Cauchemar</t>
+  </si>
+  <si>
+    <t>Revenir à l'écran titre ?</t>
+  </si>
+  <si>
+    <t>Merci d'avoir joué à la démo !
+Nous publions régulièrement les dernières nouvelles sur
+X (@Tomanegi0707) et BlueSky (@tomanegi0707.bsky.social) !
+Nous serions ravis que vous répondiez au questionnaire,
+que vous nous suiviez et ajoutiez le jeu à votre liste de souhaits !</t>
+  </si>
+  <si>
+    <t>Voulez-vous vraiment supprimer vos données de sauvegarde ?
+(Les données supprimées ne peuvent pas être récupérées.)</t>
+  </si>
+  <si>
+    <t>Revenir à la sélection du niveau ?</t>
   </si>
 </sst>
 </file>
@@ -839,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -858,10 +907,12 @@
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="38.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="38.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -913,11 +964,17 @@
       <c r="Q1" t="s">
         <v>88</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="75">
+    <row r="2" spans="1:20" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -969,8 +1026,14 @@
       <c r="Q2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="300">
+      <c r="R2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1022,8 +1085,14 @@
       <c r="Q3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="R3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="S3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1075,8 +1144,14 @@
       <c r="Q4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="R4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1128,8 +1203,14 @@
       <c r="Q5">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="R5" t="s">
+        <v>104</v>
+      </c>
+      <c r="S5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1181,8 +1262,14 @@
       <c r="Q6">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="R6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1234,8 +1321,14 @@
       <c r="Q7">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="R7" t="s">
+        <v>106</v>
+      </c>
+      <c r="S7">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1287,11 +1380,17 @@
       <c r="Q8">
         <v>13</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" t="s">
+        <v>107</v>
+      </c>
+      <c r="S8">
+        <v>14</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="337.5">
+    <row r="9" spans="1:20" ht="337.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1343,8 +1442,14 @@
       <c r="Q9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="112.5">
+      <c r="R9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="112.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1396,8 +1501,14 @@
       <c r="Q10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="37.5">
+      <c r="R10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="S10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1449,28 +1560,34 @@
       <c r="Q11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="R11" t="s">
+        <v>110</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:20">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970E6C46-8AB5-44D0-B8C7-AF6BDA1652C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB94A3F-C515-437C-824C-8C080DF49C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -530,6 +530,55 @@
   </si>
   <si>
     <t>Revenir à la sélection du niveau ?</t>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Boşluk, Enter, Sol tık…
+Konuşmayı ilerlet</t>
+  </si>
+  <si>
+    <t>W, A, S, D veya I, J, K, L… Hareket
+Shift, +… Koşma
+Fare… Etrafa bakma
+Sol tık… Etkileşim
+Sağ tık, E veya U… Eşya kullan
+F veya H… El feneri
+P, Z veya ESC… Duraklat/Devam/Geri
+Ctrl, ?… Arkana dön</t>
+  </si>
+  <si>
+    <t>Oynama süresi</t>
+  </si>
+  <si>
+    <t>Hayal</t>
+  </si>
+  <si>
+    <t>Serap</t>
+  </si>
+  <si>
+    <t>Kâbus</t>
+  </si>
+  <si>
+    <t>Ana menüye dönülsün mü?</t>
+  </si>
+  <si>
+    <t>Demo sürümünü oynadığınız için teşekkürler!
+En son haberleri düzenli olarak
+X (@Tomanegi0707) ve BlueSky (@tomanegi0707.bsky.social) üzerinden paylaşacağız!
+Anketi doldurur, bizi takip eder ve oyunu
+istek listenize eklerseniz çok seviniriz!</t>
+  </si>
+  <si>
+    <t>Kayıt verilerini gerçekten silmek istiyor musunuz?
+(Silinen veriler geri getirilemez.)</t>
+  </si>
+  <si>
+    <t>Bölüm seçimine dönülsün mü?</t>
   </si>
 </sst>
 </file>
@@ -888,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T102"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -909,10 +958,12 @@
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32.125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="38.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="38.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -970,11 +1021,17 @@
       <c r="S1" t="s">
         <v>100</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
+        <v>111</v>
+      </c>
+      <c r="U1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="75">
+    <row r="2" spans="1:22" ht="75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1032,8 +1089,14 @@
       <c r="S2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="300">
+      <c r="T2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="U2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="300">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1091,8 +1154,14 @@
       <c r="S3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="T3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="U3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1150,8 +1219,14 @@
       <c r="S4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="T4" t="s">
+        <v>115</v>
+      </c>
+      <c r="U4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1209,8 +1284,14 @@
       <c r="S5">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="T5" t="s">
+        <v>116</v>
+      </c>
+      <c r="U5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1268,8 +1349,14 @@
       <c r="S6">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="T6" t="s">
+        <v>117</v>
+      </c>
+      <c r="U6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1327,8 +1414,14 @@
       <c r="S7">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="T7" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1386,11 +1479,17 @@
       <c r="S8">
         <v>14</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="T8" t="s">
+        <v>119</v>
+      </c>
+      <c r="U8">
+        <v>14</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="337.5">
+    <row r="9" spans="1:22" ht="337.5">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1448,8 +1547,14 @@
       <c r="S9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="112.5">
+      <c r="T9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="U9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="112.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1507,8 +1612,14 @@
       <c r="S10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="37.5">
+      <c r="T10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1566,28 +1677,34 @@
       <c r="S11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="T11" t="s">
+        <v>122</v>
+      </c>
+      <c r="U11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:22">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:22">
       <c r="A14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:22">
       <c r="A15">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB94A3F-C515-437C-824C-8C080DF49C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF87B1-B566-4A68-BC67-3C31ACF96062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,6 +131,351 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Space、Enter、鼠标左键…
+推进对话</t>
+  </si>
+  <si>
+    <t>通关时间</t>
+  </si>
+  <si>
+    <t>梦想</t>
+  </si>
+  <si>
+    <t>梦幻</t>
+  </si>
+  <si>
+    <t>噩梦</t>
+  </si>
+  <si>
+    <t>要返回标题画面吗？</t>
+  </si>
+  <si>
+    <t>感谢您游玩本作的试玩版！
+我们会通过X(@Tomanegi0707)和BlueSky(@tomanegi0707.bsky.social)
+随时发布最新消息！
+如果您能填写问卷、关注我们的社交账号，
+并将本作加入愿望单，我们将不胜感激！</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Space、Enter、滑鼠左鍵…
+推進對話</t>
+  </si>
+  <si>
+    <t>通關時間</t>
+  </si>
+  <si>
+    <t>夢想</t>
+  </si>
+  <si>
+    <t>夢幻</t>
+  </si>
+  <si>
+    <t>噩夢</t>
+  </si>
+  <si>
+    <t>要返回標題畫面嗎？</t>
+  </si>
+  <si>
+    <t>感謝您遊玩本作的試玩版！
+我們會透過X(@Tomanegi0707)和BlueSky(@tomanegi0707.bsky.social)
+隨時釋出最新訊息！
+如果您能填寫問卷、關注我們的社交賬號，
+並將本作加入願望單，我們將不勝感激！</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+  </si>
+  <si>
+    <t>Espacio, Intro, clic izquierdo...
+Avanzar en la conversación.</t>
+  </si>
+  <si>
+    <t>Tiempo de finalización</t>
+  </si>
+  <si>
+    <t>Ensueño</t>
+  </si>
+  <si>
+    <t>Fantasía</t>
+  </si>
+  <si>
+    <t>Pesadilla</t>
+  </si>
+  <si>
+    <t>¿Volver a la pantalla de título?</t>
+  </si>
+  <si>
+    <t>¡Gracias por jugar la versión de demostración!
+Iremos compartiendo las últimas novedades
+en X (@Tomanegi0707) y BlueSky (@tomanegi0707.bsky.social).
+¡Nos encantaría que respondierais a la encuesta, nos siguierais en redes sociales
+y añadierais el juego a vuestra lista de deseos!</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Espaço, Enter, clique esquerdo...
+Avançar na conversa.</t>
+  </si>
+  <si>
+    <t>Tempo de conclusão</t>
+  </si>
+  <si>
+    <t>Devaneio</t>
+  </si>
+  <si>
+    <t>Fantasia</t>
+  </si>
+  <si>
+    <t>Pesadelo</t>
+  </si>
+  <si>
+    <t>Voltar para a tela de título?</t>
+  </si>
+  <si>
+    <t>Obrigado por jogar a versão demo!
+Vamos compartilhar as últimas novidades
+no X (@Tomanegi0707) e no BlueSky (@tomanegi0707.bsky.social)!
+Ficaríamos muito felizes se vocês respondessem à pesquisa, nos seguissem nas redes sociais
+e adicionassem o jogo à lista de desejos!</t>
+  </si>
+  <si>
+    <t>本当にセーブデータを削除しますか？
+(一度削除したデータは元に戻せません)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Are you sure you want to delete your save data?
+(Deleted data cannot be recovered.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>确定要删除存档吗？
+（数据一经删除将无法恢复）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確定要刪除存檔嗎？
+（資料一經刪除即無法復原）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>¿Seguro que quieres borrar los datos guardados?
+(Una vez borrados, los datos no se podrán recuperar.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tem certeza de que deseja excluir os dados salvos?
+(Uma vez excluídos, os dados não poderão ser recuperados.)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReturnToTitlePanel内とGameOver画面内</t>
+  </si>
+  <si>
+    <t>ステージ選択へ戻りますか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Return to stage selection?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返回关卡选择？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返回關卡選擇？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>¿Volver a la selección de escenario?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Voltar à seleção de fases?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Пробел, Enter, ЛКМ…
+продолжить диалог</t>
+  </si>
+  <si>
+    <t>Время прохождения</t>
+  </si>
+  <si>
+    <t>Грёза</t>
+  </si>
+  <si>
+    <t>Морок</t>
+  </si>
+  <si>
+    <t>Кошмар</t>
+  </si>
+  <si>
+    <t>Вернуться в главное меню?</t>
+  </si>
+  <si>
+    <t>Спасибо, что сыграли в демоверсию!
+Свежие новости мы публикуем в
+X (@Tomanegi0707) и BlueSky (@tomanegi0707.bsky.social)!
+Будем очень благодарны, если вы пройдёте опрос,
+подпишетесь на нас и добавите игру в список желаемого!</t>
+  </si>
+  <si>
+    <t>Вы точно хотите удалить сохранённые данные?
+(Удалённые данные восстановить нельзя.)</t>
+  </si>
+  <si>
+    <t>Вернуться к выбору этапа?</t>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Leertaste, Enter, Linksklick …
+Gespräch fortsetzen</t>
+  </si>
+  <si>
+    <t>Spielzeit</t>
+  </si>
+  <si>
+    <t>Träumerei</t>
+  </si>
+  <si>
+    <t>Trugbild</t>
+  </si>
+  <si>
+    <t>Albtraum</t>
+  </si>
+  <si>
+    <t>Zum Titelbildschirm zurückkehren?</t>
+  </si>
+  <si>
+    <t>Vielen Dank, dass du die Demo gespielt hast!
+Neuigkeiten gibt es laufend auf
+X (@Tomanegi0707) und BlueSky (@tomanegi0707.bsky.social)!
+Wir würden uns sehr freuen, wenn du an der Umfrage teilnimmst,
+uns folgst und das Spiel auf deine Wunschliste setzt!</t>
+  </si>
+  <si>
+    <t>Möchtest du deine Speicherdaten wirklich löschen?
+(Gelöschte Daten können nicht wiederhergestellt werden.)</t>
+  </si>
+  <si>
+    <t>Zur Stufenauswahl zurückkehren?</t>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>Espace, Entrée, clic gauche…
+faire avancer le dialogue</t>
+  </si>
+  <si>
+    <t>Temps de jeu</t>
+  </si>
+  <si>
+    <t>Rêverie</t>
+  </si>
+  <si>
+    <t>Chimère</t>
+  </si>
+  <si>
+    <t>Cauchemar</t>
+  </si>
+  <si>
+    <t>Revenir à l'écran titre ?</t>
+  </si>
+  <si>
+    <t>Merci d'avoir joué à la démo !
+Nous publions régulièrement les dernières nouvelles sur
+X (@Tomanegi0707) et BlueSky (@tomanegi0707.bsky.social) !
+Nous serions ravis que vous répondiez au questionnaire,
+que vous nous suiviez et ajoutiez le jeu à votre liste de souhaits !</t>
+  </si>
+  <si>
+    <t>Voulez-vous vraiment supprimer vos données de sauvegarde ?
+(Les données supprimées ne peuvent pas être récupérées.)</t>
+  </si>
+  <si>
+    <t>Revenir à la sélection du niveau ?</t>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Boşluk, Enter, Sol tık…
+Konuşmayı ilerlet</t>
+  </si>
+  <si>
+    <t>Oynama süresi</t>
+  </si>
+  <si>
+    <t>Hayal</t>
+  </si>
+  <si>
+    <t>Serap</t>
+  </si>
+  <si>
+    <t>Kâbus</t>
+  </si>
+  <si>
+    <t>Ana menüye dönülsün mü?</t>
+  </si>
+  <si>
+    <t>Demo sürümünü oynadığınız için teşekkürler!
+En son haberleri düzenli olarak
+X (@Tomanegi0707) ve BlueSky (@tomanegi0707.bsky.social) üzerinden paylaşacağız!
+Anketi doldurur, bizi takip eder ve oyunu
+istek listenize eklerseniz çok seviniriz!</t>
+  </si>
+  <si>
+    <t>Kayıt verilerini gerçekten silmek istiyor musunuz?
+(Silinen veriler geri getirilemez.)</t>
+  </si>
+  <si>
+    <t>Bölüm seçimine dönülsün mü?</t>
+  </si>
+  <si>
     <t>W,A,S,D　or　I,J,K,L…移動
 Shift, +キー…ダッシュ
 マウス移動…視点移動
@@ -138,7 +483,8 @@
 右クリック or E or U…アイテム使用
 F or H…ライト点滅
 P or Z or ESC…ポーズ/ポーズ解除/戻る
-Ctrl, ?キー…振り返る</t>
+Ctrl, ?キー…振り返る
+Q or O 長押し…アイテムを捨てる</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -150,12 +496,9 @@
 Right click or E or U… Use item
 F or H… Flashing light
 P or Z or ESC… Pause/Unpause/Back
-Ctrl, ? key… Turn around</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Space、Enter、鼠标左键…
-推进对话</t>
+Ctrl, ? key… Turn around
+Hold Q or O … Discard item</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W、A、S、D　或　I、J、K、L…移动
@@ -165,41 +508,9 @@
 鼠标右键 或 E 或 U…使用道具
 F 或 H…开关灯光
 P 或 Z 或 ESC…暂停/取消暂停/返回
-Ctrl、?键…回头</t>
-  </si>
-  <si>
-    <t>通关时间</t>
-  </si>
-  <si>
-    <t>梦想</t>
-  </si>
-  <si>
-    <t>梦幻</t>
-  </si>
-  <si>
-    <t>噩梦</t>
-  </si>
-  <si>
-    <t>要返回标题画面吗？</t>
-  </si>
-  <si>
-    <t>感谢您游玩本作的试玩版！
-我们会通过X(@Tomanegi0707)和BlueSky(@tomanegi0707.bsky.social)
-随时发布最新消息！
-如果您能填写问卷、关注我们的社交账号，
-并将本作加入愿望单，我们将不胜感激！</t>
-  </si>
-  <si>
-    <t>messageChinese01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>messageSizeChinese01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Space、Enter、滑鼠左鍵…
-推進對話</t>
+Ctrl、?键…回头
+长按 Q 或 O … 丢弃道具</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W、A、S、D　或　I、J、K、L…移動
@@ -209,101 +520,9 @@
 滑鼠右鍵 或 E 或 U…使用道具
 F 或 H…開關燈光
 P 或 Z 或 ESC…暫停/取消暫停/返回
-Ctrl、?鍵…回頭</t>
-  </si>
-  <si>
-    <t>通關時間</t>
-  </si>
-  <si>
-    <t>夢想</t>
-  </si>
-  <si>
-    <t>夢幻</t>
-  </si>
-  <si>
-    <t>噩夢</t>
-  </si>
-  <si>
-    <t>要返回標題畫面嗎？</t>
-  </si>
-  <si>
-    <t>感謝您遊玩本作的試玩版！
-我們會透過X(@Tomanegi0707)和BlueSky(@tomanegi0707.bsky.social)
-隨時釋出最新訊息！
-如果您能填寫問卷、關注我們的社交賬號，
-並將本作加入願望單，我們將不勝感激！</t>
-  </si>
-  <si>
-    <t>messageChinese02</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>messageSizeChinese02</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>messageSpanish</t>
-  </si>
-  <si>
-    <t>messageSizeSpanish</t>
-  </si>
-  <si>
-    <t>Espacio, Intro, clic izquierdo...
-Avanzar en la conversación.</t>
-  </si>
-  <si>
-    <t>Tiempo de finalización</t>
-  </si>
-  <si>
-    <t>Ensueño</t>
-  </si>
-  <si>
-    <t>Fantasía</t>
-  </si>
-  <si>
-    <t>Pesadilla</t>
-  </si>
-  <si>
-    <t>¿Volver a la pantalla de título?</t>
-  </si>
-  <si>
-    <t>¡Gracias por jugar la versión de demostración!
-Iremos compartiendo las últimas novedades
-en X (@Tomanegi0707) y BlueSky (@tomanegi0707.bsky.social).
-¡Nos encantaría que respondierais a la encuesta, nos siguierais en redes sociales
-y añadierais el juego a vuestra lista de deseos!</t>
-  </si>
-  <si>
-    <t>messagePortuguese</t>
-  </si>
-  <si>
-    <t>messageSizePortuguese</t>
-  </si>
-  <si>
-    <t>Espaço, Enter, clique esquerdo...
-Avançar na conversa.</t>
-  </si>
-  <si>
-    <t>Tempo de conclusão</t>
-  </si>
-  <si>
-    <t>Devaneio</t>
-  </si>
-  <si>
-    <t>Fantasia</t>
-  </si>
-  <si>
-    <t>Pesadelo</t>
-  </si>
-  <si>
-    <t>Voltar para a tela de título?</t>
-  </si>
-  <si>
-    <t>Obrigado por jogar a versão demo!
-Vamos compartilhar as últimas novidades
-no X (@Tomanegi0707) e no BlueSky (@tomanegi0707.bsky.social)!
-Ficaríamos muito felizes se vocês respondessem à pesquisa, nos seguissem nas redes sociais
-e adicionassem o jogo à lista de desejos!</t>
+Ctrl、?鍵…回頭
+長按 Q 或 O … 丟棄道具</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W, A, S, D o I, J, K, L... Moverse
@@ -313,7 +532,8 @@
 Clic derecho o E o U... Usar objeto
 F o H... Encender/apagar la linterna
 P, Z o ESC... Pausar/reanudar/volver
-Ctrl, tecla ?... Girarse</t>
+Ctrl, tecla ?... Girarse
+Mantener Q u O … Tirar objeto</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -324,75 +544,9 @@
 Clique direito ou E ou U... Usar item
 F ou H... Ligar/desligar a lanterna
 P, Z ou ESC... Pausar/despausar/voltar
-Ctrl, tecla ?... Virar-se</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>本当にセーブデータを削除しますか？
-(一度削除したデータは元に戻せません)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Are you sure you want to delete your save data?
-(Deleted data cannot be recovered.)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>确定要删除存档吗？
-（数据一经删除将无法恢复）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>確定要刪除存檔嗎？
-（資料一經刪除即無法復原）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>¿Seguro que quieres borrar los datos guardados?
-(Una vez borrados, los datos no se podrán recuperar.)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Tem certeza de que deseja excluir os dados salvos?
-(Uma vez excluídos, os dados não poderão ser recuperados.)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ReturnToTitlePanel内とGameOver画面内</t>
-  </si>
-  <si>
-    <t>ステージ選択へ戻りますか？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Return to stage selection?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>返回关卡选择？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>返回關卡選擇？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>¿Volver a la selección de escenario?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Voltar à seleção de fases?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>messageRussian</t>
-  </si>
-  <si>
-    <t>messageSizeRussian</t>
-  </si>
-  <si>
-    <t>Пробел, Enter, ЛКМ…
-продолжить диалог</t>
+Ctrl, tecla ?... Virar-se
+Segurar Q ou O … Descartar item</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W, A, S, D или I, J, K, L… Движение
@@ -402,46 +556,9 @@
 ПКМ, E или U… Использовать предмет
 F или H… Фонарик
 P, Z или ESC… Пауза/Продолжить/Назад
-Ctrl, ?… Оглянуться</t>
-  </si>
-  <si>
-    <t>Время прохождения</t>
-  </si>
-  <si>
-    <t>Грёза</t>
-  </si>
-  <si>
-    <t>Морок</t>
-  </si>
-  <si>
-    <t>Кошмар</t>
-  </si>
-  <si>
-    <t>Вернуться в главное меню?</t>
-  </si>
-  <si>
-    <t>Спасибо, что сыграли в демоверсию!
-Свежие новости мы публикуем в
-X (@Tomanegi0707) и BlueSky (@tomanegi0707.bsky.social)!
-Будем очень благодарны, если вы пройдёте опрос,
-подпишетесь на нас и добавите игру в список желаемого!</t>
-  </si>
-  <si>
-    <t>Вы точно хотите удалить сохранённые данные?
-(Удалённые данные восстановить нельзя.)</t>
-  </si>
-  <si>
-    <t>Вернуться к выбору этапа?</t>
-  </si>
-  <si>
-    <t>messageGerman</t>
-  </si>
-  <si>
-    <t>messageSizeGerman</t>
-  </si>
-  <si>
-    <t>Leertaste, Enter, Linksklick …
-Gespräch fortsetzen</t>
+Ctrl, ?… Оглянуться
+Удерживать Q или O … Выбросить предмет</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W, A, S, D oder I, J, K, L … Bewegen
@@ -451,46 +568,9 @@
 Rechtsklick oder E oder U … Gegenstand benutzen
 F oder H … Taschenlampe
 P oder Z oder ESC … Pause/Fortsetzen/Zurück
-Strg, ? … Umdrehen</t>
-  </si>
-  <si>
-    <t>Spielzeit</t>
-  </si>
-  <si>
-    <t>Träumerei</t>
-  </si>
-  <si>
-    <t>Trugbild</t>
-  </si>
-  <si>
-    <t>Albtraum</t>
-  </si>
-  <si>
-    <t>Zum Titelbildschirm zurückkehren?</t>
-  </si>
-  <si>
-    <t>Vielen Dank, dass du die Demo gespielt hast!
-Neuigkeiten gibt es laufend auf
-X (@Tomanegi0707) und BlueSky (@tomanegi0707.bsky.social)!
-Wir würden uns sehr freuen, wenn du an der Umfrage teilnimmst,
-uns folgst und das Spiel auf deine Wunschliste setzt!</t>
-  </si>
-  <si>
-    <t>Möchtest du deine Speicherdaten wirklich löschen?
-(Gelöschte Daten können nicht wiederhergestellt werden.)</t>
-  </si>
-  <si>
-    <t>Zur Stufenauswahl zurückkehren?</t>
-  </si>
-  <si>
-    <t>messageFrench</t>
-  </si>
-  <si>
-    <t>messageSizeFrench</t>
-  </si>
-  <si>
-    <t>Espace, Entrée, clic gauche…
-faire avancer le dialogue</t>
+Strg, ? … Umdrehen
+Q oder O gedrückt halten … Gegenstand wegwerfen</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W, A, S, D ou I, J, K, L… Se déplacer
@@ -500,46 +580,9 @@
 Clic droit, E ou U… Utiliser un objet
 F ou H… Lampe torche
 P, Z ou Échap… Pause/Reprendre/Retour
-Ctrl, ?… Se retourner</t>
-  </si>
-  <si>
-    <t>Temps de jeu</t>
-  </si>
-  <si>
-    <t>Rêverie</t>
-  </si>
-  <si>
-    <t>Chimère</t>
-  </si>
-  <si>
-    <t>Cauchemar</t>
-  </si>
-  <si>
-    <t>Revenir à l'écran titre ?</t>
-  </si>
-  <si>
-    <t>Merci d'avoir joué à la démo !
-Nous publions régulièrement les dernières nouvelles sur
-X (@Tomanegi0707) et BlueSky (@tomanegi0707.bsky.social) !
-Nous serions ravis que vous répondiez au questionnaire,
-que vous nous suiviez et ajoutiez le jeu à votre liste de souhaits !</t>
-  </si>
-  <si>
-    <t>Voulez-vous vraiment supprimer vos données de sauvegarde ?
-(Les données supprimées ne peuvent pas être récupérées.)</t>
-  </si>
-  <si>
-    <t>Revenir à la sélection du niveau ?</t>
-  </si>
-  <si>
-    <t>messageTurkish</t>
-  </si>
-  <si>
-    <t>messageSizeTurkish</t>
-  </si>
-  <si>
-    <t>Boşluk, Enter, Sol tık…
-Konuşmayı ilerlet</t>
+Ctrl, ?… Se retourner
+Maintenir Q ou O … Jeter l’objet</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W, A, S, D veya I, J, K, L… Hareket
@@ -549,36 +592,9 @@
 Sağ tık, E veya U… Eşya kullan
 F veya H… El feneri
 P, Z veya ESC… Duraklat/Devam/Geri
-Ctrl, ?… Arkana dön</t>
-  </si>
-  <si>
-    <t>Oynama süresi</t>
-  </si>
-  <si>
-    <t>Hayal</t>
-  </si>
-  <si>
-    <t>Serap</t>
-  </si>
-  <si>
-    <t>Kâbus</t>
-  </si>
-  <si>
-    <t>Ana menüye dönülsün mü?</t>
-  </si>
-  <si>
-    <t>Demo sürümünü oynadığınız için teşekkürler!
-En son haberleri düzenli olarak
-X (@Tomanegi0707) ve BlueSky (@tomanegi0707.bsky.social) üzerinden paylaşacağız!
-Anketi doldurur, bizi takip eder ve oyunu
-istek listenize eklerseniz çok seviniriz!</t>
-  </si>
-  <si>
-    <t>Kayıt verilerini gerçekten silmek istiyor musunuz?
-(Silinen veriler geri getirilemez.)</t>
-  </si>
-  <si>
-    <t>Bölüm seçimine dönülsün mü?</t>
+Ctrl, ?… Arkana dön
+Q veya O basılı tut … Eşyayı at</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -980,52 +996,52 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Q1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="R1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="S1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="T1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="U1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>15</v>
@@ -1048,114 +1064,114 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I2" s="5">
         <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K2">
         <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M2">
         <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O2">
         <v>8</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="Q2">
         <v>8</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="S2">
         <v>8</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="U2">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="300">
+    <row r="3" spans="1:22" ht="337.5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="G3" s="3">
         <v>12</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="I3" s="5">
         <v>12</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="K3">
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="M3">
         <v>8</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="O3">
         <v>8</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="Q3">
         <v>8</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="S3">
         <v>8</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="U3">
         <v>8</v>
@@ -1178,49 +1194,49 @@
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3">
         <v>16</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I4" s="5">
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K4">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M4">
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O4">
         <v>12</v>
       </c>
       <c r="P4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="Q4">
         <v>12</v>
       </c>
       <c r="R4" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S4">
         <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="U4">
         <v>12</v>
@@ -1243,49 +1259,49 @@
         <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
         <v>32</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I5" s="5">
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K5">
         <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M5">
         <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="O5">
         <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="Q5">
         <v>27</v>
       </c>
       <c r="R5" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="S5">
         <v>32</v>
       </c>
       <c r="T5" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="U5">
         <v>32</v>
@@ -1308,49 +1324,49 @@
         <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3">
         <v>32</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I6" s="5">
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K6">
         <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M6">
         <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O6">
         <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="Q6">
         <v>31</v>
       </c>
       <c r="R6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="S6">
         <v>32</v>
       </c>
       <c r="T6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="U6">
         <v>32</v>
@@ -1373,49 +1389,49 @@
         <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3">
         <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5">
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M7">
         <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="O7">
         <v>32</v>
       </c>
       <c r="P7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="Q7">
         <v>32</v>
       </c>
       <c r="R7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="S7">
         <v>31</v>
       </c>
       <c r="T7" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="U7">
         <v>32</v>
@@ -1438,55 +1454,55 @@
         <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G8" s="3">
         <v>14</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I8" s="5">
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K8">
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M8">
         <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O8">
         <v>14</v>
       </c>
       <c r="P8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="Q8">
         <v>13</v>
       </c>
       <c r="R8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="S8">
         <v>14</v>
       </c>
       <c r="T8" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="U8">
         <v>14</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="337.5">
@@ -1506,49 +1522,49 @@
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I9" s="5">
         <v>20</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K9">
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M9">
         <v>16</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="O9">
         <v>16</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="Q9">
         <v>16</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="S9">
         <v>16</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="U9">
         <v>16</v>
@@ -1559,61 +1575,61 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C10">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I10">
         <v>14</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K10">
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="Q10">
         <v>8</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="S10">
         <v>8</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1624,61 +1640,61 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E11">
         <v>12</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>14</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K11">
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M11">
         <v>10</v>
       </c>
       <c r="N11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="O11">
         <v>10</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="Q11">
         <v>10</v>
       </c>
       <c r="R11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="S11">
         <v>10</v>
       </c>
       <c r="T11" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="U11">
         <v>10</v>

--- a/Assets/Originals/Excels/UIText/UITextMessage.xlsx
+++ b/Assets/Originals/Excels/UIText/UITextMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\UIText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF87B1-B566-4A68-BC67-3C31ACF96062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8CC100-85DF-42FA-B153-F0F750CBFDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,16 +58,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Space,Enter,左クリック…
-会話を進める</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Space, Enter, Left Click... 
-To advance the conversation.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クリア時間</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -474,31 +464,6 @@
   </si>
   <si>
     <t>Bölüm seçimine dönülsün mü?</t>
-  </si>
-  <si>
-    <t>W,A,S,D　or　I,J,K,L…移動
-Shift, +キー…ダッシュ
-マウス移動…視点移動
-左クリック…インタラクト
-右クリック or E or U…アイテム使用
-F or H…ライト点滅
-P or Z or ESC…ポーズ/ポーズ解除/戻る
-Ctrl, ?キー…振り返る
-Q or O 長押し…アイテムを捨てる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>W, A, S, D or I, J, K, L… Move
-Shift, + key… Dash
-Mouse movement… 
-Camera movement
-Left click… Interact
-Right click or E or U… Use item
-F or H… Flashing light
-P or Z or ESC… Pause/Unpause/Back
-Ctrl, ? key… Turn around
-Hold Q or O … Discard item</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>W、A、S、D　或　I、J、K、L…移动
@@ -594,6 +559,41 @@
 P, Z veya ESC… Duraklat/Devam/Geri
 Ctrl, ?… Arkana dön
 Q veya O basılı tut … Eşyayı at</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Space,Enter,左クリック/×,R2…
+会話を進める</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Space, Enter, Left Click/×,R2... 
+To advance the conversation.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W,A,S,D　or　I,J,K,L/L3…移動
+Shift, +キー/L2…ダッシュ
+マウス移動/R3…視点移動
+左クリック/×…インタラクト
+右クリック or E or U/R2…アイテム使用
+F or H/L1…ライト点滅
+P or Z or ESC/OPTIONS…ポーズ/ポーズ解除/戻る
+Ctrl, ?キー/R1…振り返る
+Q or O 長押し/△…アイテムを捨てる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W, A, S, D or I, J, K, L/L3… Move
+Shift, + key/L2… Dash
+Mouse movement/R3… 
+Camera movement
+Left click/×… Interact
+Right click or E or U/R2… Use item
+F or H/L1… Flashing light
+P or Z or ESC/OPTIONS… Pause/Unpause/Back
+Ctrl, ? key/R1… Turn around
+Hold Q or O/△ … Discard item</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -996,55 +996,55 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" t="s">
-        <v>39</v>
-      </c>
       <c r="L1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="T1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="U1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="75">
@@ -1052,126 +1052,126 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="C2">
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="E2">
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I2" s="5">
         <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K2">
         <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M2">
         <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O2">
         <v>8</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Q2">
         <v>8</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S2">
         <v>8</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U2">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="337.5">
+    <row r="3" spans="1:22" ht="393.75">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G3" s="3">
         <v>12</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" s="5">
         <v>12</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K3">
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3">
         <v>8</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O3">
         <v>8</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q3">
         <v>8</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="S3">
         <v>8</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="U3">
         <v>8</v>
@@ -1182,61 +1182,61 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>16</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5">
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K4">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M4">
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O4">
         <v>12</v>
       </c>
       <c r="P4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q4">
         <v>12</v>
       </c>
       <c r="R4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S4">
         <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U4">
         <v>12</v>
@@ -1247,61 +1247,61 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3">
         <v>32</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I5" s="5">
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K5">
         <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M5">
         <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O5">
         <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q5">
         <v>27</v>
       </c>
       <c r="R5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S5">
         <v>32</v>
       </c>
       <c r="T5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U5">
         <v>32</v>
@@ -1312,61 +1312,61 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>32</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" s="5">
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O6">
         <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q6">
         <v>31</v>
       </c>
       <c r="R6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S6">
         <v>32</v>
       </c>
       <c r="T6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U6">
         <v>32</v>
@@ -1377,61 +1377,61 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3">
         <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I7" s="5">
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M7">
         <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O7">
         <v>32</v>
       </c>
       <c r="P7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q7">
         <v>32</v>
       </c>
       <c r="R7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S7">
         <v>31</v>
       </c>
       <c r="T7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="U7">
         <v>32</v>
@@ -1442,67 +1442,67 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3">
         <v>14</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I8" s="5">
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8">
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M8">
         <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O8">
         <v>14</v>
       </c>
       <c r="P8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q8">
         <v>13</v>
       </c>
       <c r="R8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S8">
         <v>14</v>
       </c>
       <c r="T8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="U8">
         <v>14</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="337.5">
@@ -1510,61 +1510,61 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9" s="5">
         <v>20</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9">
         <v>16</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M9">
         <v>16</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O9">
         <v>16</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q9">
         <v>16</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S9">
         <v>16</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U9">
         <v>16</v>
@@ -1575,61 +1575,61 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I10">
         <v>14</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K10">
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Q10">
         <v>8</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S10">
         <v>8</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1640,61 +1640,61 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11">
         <v>12</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>14</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I11">
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K11">
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M11">
         <v>10</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O11">
         <v>10</v>
       </c>
       <c r="P11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q11">
         <v>10</v>
       </c>
       <c r="R11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S11">
         <v>10</v>
       </c>
       <c r="T11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="U11">
         <v>10</v>
